--- a/tests/TC-09/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-09/results/timetable_all_departments_even.xlsx
@@ -78,14 +78,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
-        <bgColor rgb="00E0E0E0"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -177,14 +177,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -192,7 +192,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -796,26 +796,26 @@
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
       <c r="H2" s="8" t="inlineStr"/>
       <c r="I2" s="8" t="inlineStr"/>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>B1
+TUT</t>
+        </is>
+      </c>
       <c r="O2" s="8" t="inlineStr"/>
       <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
@@ -848,23 +848,23 @@
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>B1
 LEC</t>
         </is>
       </c>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="12" t="n"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -931,7 +931,7 @@
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -961,21 +961,21 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>B1
-TUT</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
+LEC</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="12" t="n"/>
       <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -1113,14 +1113,14 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="Q3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1278,26 +1278,26 @@
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
       <c r="H2" s="8" t="inlineStr"/>
       <c r="I2" s="8" t="inlineStr"/>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>B1
+TUT</t>
+        </is>
+      </c>
       <c r="O2" s="8" t="inlineStr"/>
       <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
@@ -1330,23 +1330,23 @@
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>B1
 LEC</t>
         </is>
       </c>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="12" t="n"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1413,7 +1413,7 @@
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1443,21 +1443,21 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>B1
-TUT</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
+LEC</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="12" t="n"/>
       <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -1595,14 +1595,14 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="Q3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1669,10 +1669,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1705,10 +1705,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1741,10 +1741,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1777,10 +1777,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1813,10 +1813,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1849,10 +1849,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1885,10 +1885,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1897,12 +1897,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1921,10 +1921,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1957,10 +1957,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1993,10 +1993,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2029,10 +2029,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2065,10 +2065,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2101,10 +2101,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2137,10 +2137,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2173,10 +2173,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2209,10 +2209,10 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2245,10 +2245,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2281,10 +2281,10 @@
         <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/tests/TC-09/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-09/results/timetable_all_departments_even.xlsx
@@ -137,14 +137,14 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -810,17 +810,17 @@
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>B1
-TUT</t>
-        </is>
-      </c>
+      <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="8" t="inlineStr"/>
       <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
-      <c r="S2" s="8" t="inlineStr"/>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>B1
+TUT</t>
+        </is>
+      </c>
+      <c r="S2" s="11" t="n"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
@@ -857,14 +857,9 @@
       <c r="N3" s="8" t="inlineStr"/>
       <c r="O3" s="8" t="inlineStr"/>
       <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="10" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="12" t="n"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -886,10 +881,15 @@
       <c r="C4" s="8" t="inlineStr"/>
       <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="11" t="n"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
       <c r="L4" s="9" t="inlineStr">
@@ -923,10 +923,15 @@
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="11" t="n"/>
       <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
@@ -962,15 +967,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="12" t="n"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
       <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -1113,14 +1113,15 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="Q3:S3"/>
+  <mergeCells count="3">
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="R2:S2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1292,17 +1293,17 @@
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>B1
-TUT</t>
-        </is>
-      </c>
+      <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="8" t="inlineStr"/>
       <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
-      <c r="S2" s="8" t="inlineStr"/>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>B1
+TUT</t>
+        </is>
+      </c>
+      <c r="S2" s="11" t="n"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
@@ -1339,14 +1340,9 @@
       <c r="N3" s="8" t="inlineStr"/>
       <c r="O3" s="8" t="inlineStr"/>
       <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="10" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="12" t="n"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -1368,10 +1364,15 @@
       <c r="C4" s="8" t="inlineStr"/>
       <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="11" t="n"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
       <c r="L4" s="9" t="inlineStr">
@@ -1405,10 +1406,15 @@
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="11" t="n"/>
       <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
@@ -1444,15 +1450,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="12" t="n"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
       <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
@@ -1567,7 +1568,7 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -1595,14 +1596,15 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="Q3:S3"/>
+  <mergeCells count="3">
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="R2:S2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1669,10 +1671,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1705,10 +1707,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1717,7 +1719,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1741,10 +1743,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1753,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1774,13 +1776,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1789,7 +1791,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1810,13 +1812,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1825,7 +1827,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1846,13 +1848,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1861,7 +1863,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1882,7 +1884,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
@@ -1897,7 +1899,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1918,7 +1920,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
@@ -1933,7 +1935,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1954,7 +1956,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -1969,7 +1971,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1993,10 +1995,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2029,10 +2031,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2041,7 +2043,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2065,10 +2067,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2077,7 +2079,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2098,13 +2100,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2134,13 +2136,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2149,7 +2151,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2170,13 +2172,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2185,7 +2187,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2206,7 +2208,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
@@ -2242,7 +2244,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
         <v>4</v>
@@ -2257,7 +2259,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2278,7 +2280,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
         <v>4</v>
@@ -2293,7 +2295,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
